--- a/results/recurrence/glass_recurrence_scores_out_of_fold.xlsx
+++ b/results/recurrence/glass_recurrence_scores_out_of_fold.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PATIENT_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SAMPLE_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SAMPLE_TYPE</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>UP_SCORE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>DOWN_SCORE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RECURRENCE_SCORE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FOLD</t>
         </is>
@@ -478,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -507,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -536,7 +524,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -565,7 +553,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -594,7 +582,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -623,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -652,7 +640,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -681,7 +669,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -710,7 +698,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -739,7 +727,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -768,7 +756,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -797,7 +785,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -826,7 +814,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -855,7 +843,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -884,7 +872,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -913,7 +901,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -942,7 +930,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -971,7 +959,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1000,7 +988,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1029,7 +1017,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1058,7 +1046,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1087,7 +1075,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1116,7 +1104,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1145,7 +1133,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1174,7 +1162,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1203,7 +1191,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1232,7 +1220,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1261,7 +1249,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1290,7 +1278,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1319,7 +1307,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1348,7 +1336,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1377,7 +1365,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1406,7 +1394,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1435,7 +1423,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1464,7 +1452,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1493,7 +1481,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1522,7 +1510,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1551,7 +1539,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1580,7 +1568,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1609,7 +1597,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1638,7 +1626,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1667,7 +1655,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1696,7 +1684,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1725,7 +1713,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1754,7 +1742,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1783,7 +1771,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1812,7 +1800,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1841,7 +1829,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1870,7 +1858,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1899,7 +1887,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1928,7 +1916,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1957,7 +1945,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1986,7 +1974,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2015,7 +2003,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2044,7 +2032,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2073,7 +2061,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2102,7 +2090,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2131,7 +2119,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2160,7 +2148,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2189,7 +2177,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2218,7 +2206,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2247,7 +2235,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2276,7 +2264,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2305,7 +2293,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2334,7 +2322,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2363,7 +2351,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2392,7 +2380,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2421,7 +2409,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2450,7 +2438,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2479,7 +2467,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2508,7 +2496,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2537,7 +2525,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2566,7 +2554,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2595,7 +2583,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2624,7 +2612,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2653,7 +2641,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -2682,7 +2670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2711,7 +2699,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -2740,7 +2728,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2769,7 +2757,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2798,7 +2786,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2827,7 +2815,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2856,7 +2844,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2885,7 +2873,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2914,7 +2902,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2943,7 +2931,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -2972,7 +2960,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3001,7 +2989,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3030,7 +3018,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3059,7 +3047,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3088,7 +3076,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3117,7 +3105,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3146,7 +3134,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3175,7 +3163,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3204,7 +3192,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3233,7 +3221,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3262,7 +3250,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3291,7 +3279,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3320,7 +3308,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3349,7 +3337,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3378,7 +3366,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3407,7 +3395,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3436,7 +3424,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -3465,7 +3453,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -3494,7 +3482,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -3523,7 +3511,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -3552,7 +3540,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -3581,7 +3569,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -3610,7 +3598,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -3639,7 +3627,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -3668,7 +3656,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3697,7 +3685,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3726,7 +3714,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -3755,7 +3743,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -3784,7 +3772,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -3813,7 +3801,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -3842,7 +3830,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3871,7 +3859,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -3900,7 +3888,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3929,7 +3917,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -3958,7 +3946,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -3987,7 +3975,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4016,7 +4004,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4045,7 +4033,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4074,7 +4062,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4103,7 +4091,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4132,7 +4120,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4161,7 +4149,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4190,7 +4178,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4219,7 +4207,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -4248,7 +4236,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -4277,7 +4265,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -4306,7 +4294,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -4335,7 +4323,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -4364,7 +4352,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -4393,7 +4381,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -4422,7 +4410,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -4451,7 +4439,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -4480,7 +4468,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -4509,7 +4497,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4538,7 +4526,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -4567,7 +4555,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -4596,7 +4584,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -4625,7 +4613,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -4654,7 +4642,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -4683,7 +4671,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -4712,7 +4700,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -4741,7 +4729,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -4770,7 +4758,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -4799,7 +4787,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -4828,7 +4816,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4857,7 +4845,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -4886,7 +4874,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -4915,7 +4903,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -4944,7 +4932,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4973,7 +4961,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5002,7 +4990,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5031,7 +5019,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5060,7 +5048,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -5089,7 +5077,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -5118,7 +5106,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -5147,7 +5135,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -5176,7 +5164,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -5205,7 +5193,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -5234,7 +5222,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -5263,7 +5251,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -5292,7 +5280,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -5321,7 +5309,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -5350,7 +5338,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -5379,7 +5367,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -5408,7 +5396,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -5437,7 +5425,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -5466,7 +5454,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -5495,7 +5483,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -5524,7 +5512,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -5553,7 +5541,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -5582,7 +5570,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -5611,7 +5599,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -5640,7 +5628,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -5669,7 +5657,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -5698,7 +5686,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -5727,7 +5715,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -5756,7 +5744,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -5785,7 +5773,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -5814,7 +5802,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -5843,7 +5831,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Tumor Primary</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -5872,7 +5860,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -5901,7 +5889,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -5930,7 +5918,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -5959,7 +5947,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -5988,7 +5976,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -6017,7 +6005,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -6046,7 +6034,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -6075,7 +6063,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -6104,7 +6092,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -6133,7 +6121,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -6162,7 +6150,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -6191,7 +6179,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -6220,7 +6208,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -6249,7 +6237,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -6278,7 +6266,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -6307,7 +6295,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -6336,7 +6324,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -6365,7 +6353,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -6394,7 +6382,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -6423,7 +6411,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>First Recurrence</t>
         </is>
       </c>
       <c r="D207" t="n">

--- a/results/recurrence/glass_recurrence_scores_out_of_fold.xlsx
+++ b/results/recurrence/glass_recurrence_scores_out_of_fold.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PATIENT_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>SAMPLE_ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>SAMPLE_TYPE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>UP_SCORE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>DOWN_SCORE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RECURRENCE_SCORE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>FOLD</t>
         </is>
